--- a/data/ams_weekly_data/White_Mulberry/Sponsored_Brands_Campaign_report.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/Sponsored_Brands_Campaign_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\ams\AMS\AMS\CRPL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\ams_weekly_data\White_Mulberry\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A6C1BA8-10BE-4B0C-B555-0E85E579FCB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E81D1F-2C62-4D5F-997E-3D1F7E1921A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
